--- a/site/exports/ouc-coas-oceanography.xlsx
+++ b/site/exports/ouc-coas-oceanography.xlsx
@@ -453,7 +453,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分公开职业资料；非完整履历或当前人事在岗证明；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：海浪理论与计算原理、海洋要素计算与预报、海洋波动；讲授；教学／课程开设时间：时间未披露；官方页讲授课程栏；不推授课年份或现期开课，不是本人学习经历。；来源ID：ouc-guanchanglong-profile-cn；https://coas.ouc.edu.cn/2017/0310/c8869a59952/page.psp</t>
+          <t>分批核实资料，不是完整名录；部分公开职业资料；非完整履历或当前人事在岗证明；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：海浪理论与计算原理、海洋要素计算与预报、海洋波动；讲授；教学／课程开设时间：时间未披露；官方页讲授课程栏；不推授课年份或现期开课，不是本人学习经历。；来源ID：ouc-guanchanglong-profile-cn；https://coas.ouc.edu.cn/2017/0310/c8869a59952/page.psp；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -592,7 +592,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分公开职业资料；非完整履历或当前人事在岗证明；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：海洋调查方法；讲授；教学／课程开设时间：时间未披露；官方页讲授课程栏；不推授课年份或现期开课，不是本人学习经历。；来源ID：ouc-baoxianwen-profile-cn；https://coas.ouc.edu.cn/2017/0309/c8869a59894/page.psp</t>
+          <t>分批核实资料，不是完整名录；部分公开职业资料；非完整履历或当前人事在岗证明；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：海洋调查方法；讲授；教学／课程开设时间：时间未披露；官方页讲授课程栏；不推授课年份或现期开课，不是本人学习经历。；来源ID：ouc-baoxianwen-profile-cn；https://coas.ouc.edu.cn/2017/0309/c8869a59894/page.psp；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
